--- a/Excel/CondtionalFormtting.xlsx
+++ b/Excel/CondtionalFormtting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B962BB32-1578-418A-9331-E57C2A7D27BE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AB1F15-5DCC-40E4-9CE9-81A0CA2C9FAC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13660" windowHeight="4950" activeTab="1" xr2:uid="{8512916D-F948-4B8E-B259-202EB8B6061F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13660" windowHeight="4950" firstSheet="4" activeTab="5" xr2:uid="{8512916D-F948-4B8E-B259-202EB8B6061F}"/>
   </bookViews>
   <sheets>
     <sheet name="Agenda" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="HighlightEntireRow" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">HighlightEntireRow!$A$1:$D$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TopBottomRule!$B$2:$D$14</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="172">
   <si>
     <t>Conditional Formatting</t>
   </si>
@@ -240,6 +241,315 @@
   </si>
   <si>
     <t>Bottom 25%</t>
+  </si>
+  <si>
+    <t>Emp Name</t>
+  </si>
+  <si>
+    <t>Dt. Of Joining</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Ahlam Aby</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Alicia A. Elmasian</t>
+  </si>
+  <si>
+    <t>Alison Johnson</t>
+  </si>
+  <si>
+    <t>Customer Support</t>
+  </si>
+  <si>
+    <t>Alyssa Adefioye</t>
+  </si>
+  <si>
+    <t>Ann Sharp</t>
+  </si>
+  <si>
+    <t>Benny Erwin</t>
+  </si>
+  <si>
+    <t>Benny Melendez</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Brian M Stucki</t>
+  </si>
+  <si>
+    <t>Brian Tomasevic</t>
+  </si>
+  <si>
+    <t>Bryan Anderson</t>
+  </si>
+  <si>
+    <t>Bryan Brier</t>
+  </si>
+  <si>
+    <t>Cassandra Perry</t>
+  </si>
+  <si>
+    <t>Christopher Battah</t>
+  </si>
+  <si>
+    <t>Cindy Summerville</t>
+  </si>
+  <si>
+    <t>Corine M. Henderson</t>
+  </si>
+  <si>
+    <t>Cristhian Roth</t>
+  </si>
+  <si>
+    <t>Donna K. Bulgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elena Miriam Hillen </t>
+  </si>
+  <si>
+    <t>Elena Miriam Takahashi</t>
+  </si>
+  <si>
+    <t>Elena Miriam Woodburn</t>
+  </si>
+  <si>
+    <t>Eric W. Kilbride</t>
+  </si>
+  <si>
+    <t>Erik G. Rinehart</t>
+  </si>
+  <si>
+    <t>Ernest Talia</t>
+  </si>
+  <si>
+    <t>Ernest Trent</t>
+  </si>
+  <si>
+    <t>Gabriel R. Self</t>
+  </si>
+  <si>
+    <t>Genevieve   Knapp</t>
+  </si>
+  <si>
+    <t>Grant Tomasevic</t>
+  </si>
+  <si>
+    <t>Harman Abraha</t>
+  </si>
+  <si>
+    <t>Heela Kraft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ian Helmer </t>
+  </si>
+  <si>
+    <t>Jacqueline N. Gappy</t>
+  </si>
+  <si>
+    <t>Jacqueline N. Hildebrand</t>
+  </si>
+  <si>
+    <t>James Oberndorfer</t>
+  </si>
+  <si>
+    <t>James Wilson</t>
+  </si>
+  <si>
+    <t>Janalee Eggleston</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Jena Coon</t>
+  </si>
+  <si>
+    <t>Jeremiah De Grazia</t>
+  </si>
+  <si>
+    <t>Jesse Wooten</t>
+  </si>
+  <si>
+    <t>Jessica Rodriguez</t>
+  </si>
+  <si>
+    <t>Joeanne Melendez</t>
+  </si>
+  <si>
+    <t>John  Michael</t>
+  </si>
+  <si>
+    <t>Johnathan A Wilhite</t>
+  </si>
+  <si>
+    <t>Jonathan C. Parnell</t>
+  </si>
+  <si>
+    <t>Joshua Daniel</t>
+  </si>
+  <si>
+    <t>Joshua Fields</t>
+  </si>
+  <si>
+    <t>Joshua Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia  Hegwood </t>
+  </si>
+  <si>
+    <t>Julie Harken</t>
+  </si>
+  <si>
+    <t>Julie Yost</t>
+  </si>
+  <si>
+    <t>Katherine Battah</t>
+  </si>
+  <si>
+    <t>Kelley Reneau</t>
+  </si>
+  <si>
+    <t>Kelly Queen</t>
+  </si>
+  <si>
+    <t>Kevin Nevandro</t>
+  </si>
+  <si>
+    <t>Krisaundra Hightower</t>
+  </si>
+  <si>
+    <t>Laura Aguirre</t>
+  </si>
+  <si>
+    <t>Laura S Greenwell</t>
+  </si>
+  <si>
+    <t>Manuel Steele</t>
+  </si>
+  <si>
+    <t>Margaret Pavlovich</t>
+  </si>
+  <si>
+    <t>Martie Elmasian</t>
+  </si>
+  <si>
+    <t>Marylou M. Diaz</t>
+  </si>
+  <si>
+    <t>Matthew H. Rios</t>
+  </si>
+  <si>
+    <t>Matthew Tait</t>
+  </si>
+  <si>
+    <t>Matthew W Yamaguchi</t>
+  </si>
+  <si>
+    <t>Melissa Torruella</t>
+  </si>
+  <si>
+    <t>Micah Chokeir</t>
+  </si>
+  <si>
+    <t>Micah Talia</t>
+  </si>
+  <si>
+    <t>Michelle  Greenwell</t>
+  </si>
+  <si>
+    <t>Michelle  Shevlin</t>
+  </si>
+  <si>
+    <t>Moriel Caldwell</t>
+  </si>
+  <si>
+    <t>Natalie H. Woodford</t>
+  </si>
+  <si>
+    <t>Natalie H. Zeidell</t>
+  </si>
+  <si>
+    <t>Pavan Lalwani</t>
+  </si>
+  <si>
+    <t>Rebecca L. Haight</t>
+  </si>
+  <si>
+    <t>Rebecca Negrete</t>
+  </si>
+  <si>
+    <t>Ricardo Bergman</t>
+  </si>
+  <si>
+    <t>Ricardo Sherrell</t>
+  </si>
+  <si>
+    <t>Richard  Garza</t>
+  </si>
+  <si>
+    <t>Rikkie J Mahone</t>
+  </si>
+  <si>
+    <t>Rosa I. Peralta</t>
+  </si>
+  <si>
+    <t>Rose Moreno</t>
+  </si>
+  <si>
+    <t>Roshan Coon</t>
+  </si>
+  <si>
+    <t>Ryan  Mesko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Kennedy </t>
+  </si>
+  <si>
+    <t>Saif Perrine</t>
+  </si>
+  <si>
+    <t>Sara Webb</t>
+  </si>
+  <si>
+    <t>Saxton Peterson</t>
+  </si>
+  <si>
+    <t>Shireen Battah</t>
+  </si>
+  <si>
+    <t>Stacy L Chen</t>
+  </si>
+  <si>
+    <t>Stephen H. Thomas</t>
+  </si>
+  <si>
+    <t>Steven  Bolin</t>
+  </si>
+  <si>
+    <t>Tamara Pacheco</t>
+  </si>
+  <si>
+    <t>Tiffany M Blake</t>
+  </si>
+  <si>
+    <t>Tony Merrick</t>
+  </si>
+  <si>
+    <t>William Melendez</t>
+  </si>
+  <si>
+    <t>Willow Nevandro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yvette Hurtado </t>
   </si>
 </sst>
 </file>
@@ -270,7 +580,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,6 +590,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -334,11 +650,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="9">
     <dxf>
       <font>
         <color theme="1"/>
@@ -408,269 +727,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1303,27 +1359,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"Kolkata"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E13">
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F13">
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2085,9 +2141,1374 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A716E025-9B0C-4EE8-8AB0-58CF02E014DC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="4">
+        <v>43290</v>
+      </c>
+      <c r="D2" s="4">
+        <v>33869</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="4">
+        <v>43125</v>
+      </c>
+      <c r="D3" s="4">
+        <v>32686</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="4">
+        <v>40311</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="4">
+        <v>42777</v>
+      </c>
+      <c r="D5" s="4">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="4">
+        <v>42402</v>
+      </c>
+      <c r="D6" s="4">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="4">
+        <v>44168</v>
+      </c>
+      <c r="D7" s="4">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="4">
+        <v>43371</v>
+      </c>
+      <c r="D8" s="4">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="4">
+        <v>40673</v>
+      </c>
+      <c r="D9" s="4">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43403</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="4">
+        <v>40822</v>
+      </c>
+      <c r="D11" s="4">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="4">
+        <v>43678</v>
+      </c>
+      <c r="D12" s="4">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4">
+        <v>43623</v>
+      </c>
+      <c r="D13" s="4">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="4">
+        <v>43233</v>
+      </c>
+      <c r="D14" s="4">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="4">
+        <v>40717</v>
+      </c>
+      <c r="D15" s="4">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="4">
+        <v>40397</v>
+      </c>
+      <c r="D16" s="4">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="4">
+        <v>40635</v>
+      </c>
+      <c r="D17" s="4">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="4">
+        <v>42970</v>
+      </c>
+      <c r="D18" s="4">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="4">
+        <v>40838</v>
+      </c>
+      <c r="D19" s="4">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="4">
+        <v>42496</v>
+      </c>
+      <c r="D20" s="4">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="4">
+        <v>42072</v>
+      </c>
+      <c r="D21" s="4">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="4">
+        <v>42272</v>
+      </c>
+      <c r="D22" s="4">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="4">
+        <v>44139</v>
+      </c>
+      <c r="D23" s="4">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="4">
+        <v>43358</v>
+      </c>
+      <c r="D24" s="4">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="4">
+        <v>42911</v>
+      </c>
+      <c r="D25" s="4">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="4">
+        <v>44235</v>
+      </c>
+      <c r="D26" s="4">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="4">
+        <v>42462</v>
+      </c>
+      <c r="D27" s="4">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="4">
+        <v>43129</v>
+      </c>
+      <c r="D28" s="4">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="4">
+        <v>44033</v>
+      </c>
+      <c r="D29" s="4">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="4">
+        <v>43442</v>
+      </c>
+      <c r="D30" s="4">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="4">
+        <v>43447</v>
+      </c>
+      <c r="D31" s="4">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="4">
+        <v>43980</v>
+      </c>
+      <c r="D32" s="4">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="4">
+        <v>42593</v>
+      </c>
+      <c r="D33" s="4">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="4">
+        <v>43216</v>
+      </c>
+      <c r="D34" s="4">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="4">
+        <v>44199</v>
+      </c>
+      <c r="D35" s="4">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="4">
+        <v>40837</v>
+      </c>
+      <c r="D36" s="4">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="4">
+        <v>42914</v>
+      </c>
+      <c r="D37" s="4">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="4">
+        <v>40429</v>
+      </c>
+      <c r="D38" s="4">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D39" s="4">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="4">
+        <v>43160</v>
+      </c>
+      <c r="D40" s="4">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="4">
+        <v>40667</v>
+      </c>
+      <c r="D41" s="4">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="4">
+        <v>42813</v>
+      </c>
+      <c r="D42" s="4">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="4">
+        <v>43624</v>
+      </c>
+      <c r="D43" s="4">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D44" s="4">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="4">
+        <v>43912</v>
+      </c>
+      <c r="D45" s="4">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" s="4">
+        <v>43053</v>
+      </c>
+      <c r="D46" s="4">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="4">
+        <v>42615</v>
+      </c>
+      <c r="D47" s="4">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="4">
+        <v>40414</v>
+      </c>
+      <c r="D48" s="4">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D49" s="4">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="4">
+        <v>44142</v>
+      </c>
+      <c r="D50" s="4">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="4">
+        <v>42067</v>
+      </c>
+      <c r="D51" s="4">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="4">
+        <v>42378</v>
+      </c>
+      <c r="D52" s="4">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4">
+        <v>40556</v>
+      </c>
+      <c r="D53" s="4">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="4">
+        <v>42954</v>
+      </c>
+      <c r="D54" s="4">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="4">
+        <v>42129</v>
+      </c>
+      <c r="D55" s="4">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="4">
+        <v>42220</v>
+      </c>
+      <c r="D56" s="4">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="4">
+        <v>42477</v>
+      </c>
+      <c r="D57" s="4">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="4">
+        <v>44382</v>
+      </c>
+      <c r="D58" s="4">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="4">
+        <v>42936</v>
+      </c>
+      <c r="D59" s="4">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="4">
+        <v>40519</v>
+      </c>
+      <c r="D60" s="4">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="4">
+        <v>42841</v>
+      </c>
+      <c r="D61" s="4">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="4">
+        <v>42995</v>
+      </c>
+      <c r="D62" s="4">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="4">
+        <v>44243</v>
+      </c>
+      <c r="D63" s="4">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="4">
+        <v>42144</v>
+      </c>
+      <c r="D64" s="4">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="4">
+        <v>42296</v>
+      </c>
+      <c r="D65" s="4">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D66" s="4">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="4">
+        <v>43791</v>
+      </c>
+      <c r="D67" s="4">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="4">
+        <v>44131</v>
+      </c>
+      <c r="D68" s="4">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="4">
+        <v>42428</v>
+      </c>
+      <c r="D69" s="4">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="4">
+        <v>42690</v>
+      </c>
+      <c r="D70" s="4">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="4">
+        <v>42359</v>
+      </c>
+      <c r="D71" s="4">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="4">
+        <v>40840</v>
+      </c>
+      <c r="D72" s="4">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="4">
+        <v>40880</v>
+      </c>
+      <c r="D73" s="4">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="4">
+        <v>42049</v>
+      </c>
+      <c r="D74" s="4">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="4">
+        <v>43582</v>
+      </c>
+      <c r="D75" s="4">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="4">
+        <v>43034</v>
+      </c>
+      <c r="D76" s="4">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="4">
+        <v>43060</v>
+      </c>
+      <c r="D77" s="4">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="4">
+        <v>43846</v>
+      </c>
+      <c r="D78" s="4">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="4">
+        <v>44162</v>
+      </c>
+      <c r="D79" s="4">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="4">
+        <v>43788</v>
+      </c>
+      <c r="D80" s="4">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="4">
+        <v>42864</v>
+      </c>
+      <c r="D81" s="4">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C82" s="4">
+        <v>42856</v>
+      </c>
+      <c r="D82" s="4">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" s="4">
+        <v>44122</v>
+      </c>
+      <c r="D83" s="4">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="4">
+        <v>40901</v>
+      </c>
+      <c r="D84" s="4">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="4">
+        <v>42430</v>
+      </c>
+      <c r="D85" s="4">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="4">
+        <v>43017</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="4">
+        <v>43174</v>
+      </c>
+      <c r="D87" s="4">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="4">
+        <v>43951</v>
+      </c>
+      <c r="D88" s="4">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="4">
+        <v>40870</v>
+      </c>
+      <c r="D89" s="4">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C90" s="4">
+        <v>42726</v>
+      </c>
+      <c r="D90" s="4">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="4">
+        <v>44229</v>
+      </c>
+      <c r="D91" s="4">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" s="4">
+        <v>42088</v>
+      </c>
+      <c r="D92" s="4">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C93" s="4">
+        <v>43218</v>
+      </c>
+      <c r="D93" s="4">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C94" s="4">
+        <v>40804</v>
+      </c>
+      <c r="D94" s="4">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C95" s="4">
+        <v>43609</v>
+      </c>
+      <c r="D95" s="4">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="4">
+        <v>40469</v>
+      </c>
+      <c r="D96" s="4">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" s="4">
+        <v>44179</v>
+      </c>
+      <c r="D97" s="4">
+        <v>30335</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel/CondtionalFormtting.xlsx
+++ b/Excel/CondtionalFormtting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AB1F15-5DCC-40E4-9CE9-81A0CA2C9FAC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A2BD10-ADA9-4C26-BA28-F7380C44594F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13660" windowHeight="4950" firstSheet="4" activeTab="5" xr2:uid="{8512916D-F948-4B8E-B259-202EB8B6061F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13660" windowHeight="4950" firstSheet="6" activeTab="9" xr2:uid="{8512916D-F948-4B8E-B259-202EB8B6061F}"/>
   </bookViews>
   <sheets>
     <sheet name="Agenda" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,15 @@
     <sheet name="ColorScales" sheetId="4" r:id="rId4"/>
     <sheet name="TopBottomRule" sheetId="5" r:id="rId5"/>
     <sheet name="HighlightEntireRow" sheetId="6" r:id="rId6"/>
+    <sheet name="HER" sheetId="7" r:id="rId7"/>
+    <sheet name="HER2" sheetId="8" r:id="rId8"/>
+    <sheet name="HER3" sheetId="9" r:id="rId9"/>
+    <sheet name="HER4" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'HER2'!$A$1:$D$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'HER3'!$A$1:$D$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'HER4'!$A$1:$D$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">HighlightEntireRow!$A$1:$D$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TopBottomRule!$B$2:$D$14</definedName>
   </definedNames>
@@ -34,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="176">
   <si>
     <t>Conditional Formatting</t>
   </si>
@@ -550,13 +557,25 @@
   </si>
   <si>
     <t xml:space="preserve">Yvette Hurtado </t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,8 +598,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -590,6 +617,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -650,14 +683,468 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="49">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFED7D31"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFED7D31"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -1124,6 +1611,1430 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C232EA-3CBF-4C0B-A208-AB546DD7B881}">
+  <dimension ref="A1:G97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10251</v>
+      </c>
+      <c r="E2" t="e">
+        <f ca="1">unique(A2:A97)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="4">
+        <v>42477</v>
+      </c>
+      <c r="D3" s="4">
+        <v>10356</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="4">
+        <v>42864</v>
+      </c>
+      <c r="D4" s="4">
+        <v>10953</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="4">
+        <v>43624</v>
+      </c>
+      <c r="D5" s="4">
+        <v>11787</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="4">
+        <v>44122</v>
+      </c>
+      <c r="D6" s="4">
+        <v>17520</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="4">
+        <v>42690</v>
+      </c>
+      <c r="D7" s="4">
+        <v>18320</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="4">
+        <v>42970</v>
+      </c>
+      <c r="D8" s="4">
+        <v>21921</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="4">
+        <v>40880</v>
+      </c>
+      <c r="D9" s="4">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="4">
+        <v>42615</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="4">
+        <v>44229</v>
+      </c>
+      <c r="D11" s="4">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D12" s="4">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="4">
+        <v>43609</v>
+      </c>
+      <c r="D13" s="4">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="4">
+        <v>42378</v>
+      </c>
+      <c r="D14" s="4">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="4">
+        <v>43358</v>
+      </c>
+      <c r="D15" s="4">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="4">
+        <v>40429</v>
+      </c>
+      <c r="D16" s="4">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="4">
+        <v>43216</v>
+      </c>
+      <c r="D17" s="4">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="4">
+        <v>43160</v>
+      </c>
+      <c r="D18" s="4">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="4">
+        <v>44199</v>
+      </c>
+      <c r="D19" s="4">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="4">
+        <v>43218</v>
+      </c>
+      <c r="D20" s="4">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C21" s="4">
+        <v>43788</v>
+      </c>
+      <c r="D21" s="4">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4">
+        <v>42593</v>
+      </c>
+      <c r="D22" s="4">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="4">
+        <v>43371</v>
+      </c>
+      <c r="D23" s="4">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="4">
+        <v>43053</v>
+      </c>
+      <c r="D24" s="4">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="4">
+        <v>43846</v>
+      </c>
+      <c r="D25" s="4">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="4">
+        <v>43912</v>
+      </c>
+      <c r="D26" s="4">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="4">
+        <v>42911</v>
+      </c>
+      <c r="D27" s="4">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="4">
+        <v>43980</v>
+      </c>
+      <c r="D28" s="4">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="4">
+        <v>43129</v>
+      </c>
+      <c r="D29" s="4">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D30" s="4">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" s="4">
+        <v>40840</v>
+      </c>
+      <c r="D31" s="4">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="4">
+        <v>42777</v>
+      </c>
+      <c r="D32" s="4">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="4">
+        <v>43233</v>
+      </c>
+      <c r="D33" s="4">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="4">
+        <v>42995</v>
+      </c>
+      <c r="D34" s="4">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="4">
+        <v>42296</v>
+      </c>
+      <c r="D35" s="4">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="4">
+        <v>42936</v>
+      </c>
+      <c r="D36" s="4">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="4">
+        <v>42496</v>
+      </c>
+      <c r="D37" s="4">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="4">
+        <v>42914</v>
+      </c>
+      <c r="D38" s="4">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" s="4">
+        <v>43791</v>
+      </c>
+      <c r="D39" s="4">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="4">
+        <v>40673</v>
+      </c>
+      <c r="D40" s="4">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="4">
+        <v>42144</v>
+      </c>
+      <c r="D41" s="4">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="4">
+        <v>40414</v>
+      </c>
+      <c r="D42" s="4">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="4">
+        <v>44033</v>
+      </c>
+      <c r="D43" s="4">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="4">
+        <v>40837</v>
+      </c>
+      <c r="D44" s="4">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="4">
+        <v>42462</v>
+      </c>
+      <c r="D45" s="4">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="4">
+        <v>40717</v>
+      </c>
+      <c r="D46" s="4">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" s="4">
+        <v>42129</v>
+      </c>
+      <c r="D47" s="4">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C48" s="4">
+        <v>40804</v>
+      </c>
+      <c r="D48" s="4">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="4">
+        <v>43623</v>
+      </c>
+      <c r="D49" s="4">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="4">
+        <v>42359</v>
+      </c>
+      <c r="D50" s="4">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="4">
+        <v>42856</v>
+      </c>
+      <c r="D51" s="4">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" s="4">
+        <v>44382</v>
+      </c>
+      <c r="D52" s="4">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="4">
+        <v>43442</v>
+      </c>
+      <c r="D53" s="4">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="4">
+        <v>44179</v>
+      </c>
+      <c r="D54" s="4">
+        <v>30335</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C55" s="4">
+        <v>42726</v>
+      </c>
+      <c r="D55" s="4">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="4">
+        <v>42220</v>
+      </c>
+      <c r="D56" s="4">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="4">
+        <v>43951</v>
+      </c>
+      <c r="D57" s="4">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="4">
+        <v>43447</v>
+      </c>
+      <c r="D58" s="4">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="4">
+        <v>43403</v>
+      </c>
+      <c r="D59" s="4">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" s="4">
+        <v>40901</v>
+      </c>
+      <c r="D60" s="4">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="4">
+        <v>44162</v>
+      </c>
+      <c r="D61" s="4">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="4">
+        <v>43125</v>
+      </c>
+      <c r="D62" s="4">
+        <v>32686</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="4">
+        <v>42272</v>
+      </c>
+      <c r="D63" s="4">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="4">
+        <v>42841</v>
+      </c>
+      <c r="D64" s="4">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="4">
+        <v>40556</v>
+      </c>
+      <c r="D65" s="4">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" s="4">
+        <v>44235</v>
+      </c>
+      <c r="D66" s="4">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="4">
+        <v>43290</v>
+      </c>
+      <c r="D67" s="4">
+        <v>33869</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C68" s="4">
+        <v>43034</v>
+      </c>
+      <c r="D68" s="4">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="4">
+        <v>44168</v>
+      </c>
+      <c r="D69" s="4">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" s="4">
+        <v>43174</v>
+      </c>
+      <c r="D70" s="4">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="4">
+        <v>44131</v>
+      </c>
+      <c r="D71" s="4">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C72" s="4">
+        <v>40667</v>
+      </c>
+      <c r="D72" s="4">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" s="4">
+        <v>42072</v>
+      </c>
+      <c r="D73" s="4">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="4">
+        <v>42049</v>
+      </c>
+      <c r="D74" s="4">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="4">
+        <v>42430</v>
+      </c>
+      <c r="D75" s="4">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="4">
+        <v>40822</v>
+      </c>
+      <c r="D76" s="4">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="4">
+        <v>42402</v>
+      </c>
+      <c r="D77" s="4">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="4">
+        <v>40838</v>
+      </c>
+      <c r="D78" s="4">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C79" s="4">
+        <v>44142</v>
+      </c>
+      <c r="D79" s="4">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" s="4">
+        <v>42954</v>
+      </c>
+      <c r="D80" s="4">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="4">
+        <v>40397</v>
+      </c>
+      <c r="D81" s="4">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="4">
+        <v>40635</v>
+      </c>
+      <c r="D82" s="4">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C83" s="4">
+        <v>42428</v>
+      </c>
+      <c r="D83" s="4">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C84" s="4">
+        <v>42067</v>
+      </c>
+      <c r="D84" s="4">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C85" s="4">
+        <v>43582</v>
+      </c>
+      <c r="D85" s="4">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C86" s="4">
+        <v>42813</v>
+      </c>
+      <c r="D86" s="4">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D87" s="4">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C88" s="4">
+        <v>42088</v>
+      </c>
+      <c r="D88" s="4">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89" s="4">
+        <v>43678</v>
+      </c>
+      <c r="D89" s="4">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C90" s="4">
+        <v>43060</v>
+      </c>
+      <c r="D90" s="4">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C91" s="4">
+        <v>40311</v>
+      </c>
+      <c r="D91" s="4">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C92" s="4">
+        <v>43017</v>
+      </c>
+      <c r="D92" s="4">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" s="4">
+        <v>40469</v>
+      </c>
+      <c r="D93" s="4">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C94" s="4">
+        <v>40519</v>
+      </c>
+      <c r="D94" s="4">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95" s="4">
+        <v>44139</v>
+      </c>
+      <c r="D95" s="4">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C96" s="4">
+        <v>44243</v>
+      </c>
+      <c r="D96" s="4">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C97" s="4">
+        <v>40870</v>
+      </c>
+      <c r="D97" s="4">
+        <v>49204</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D97" xr:uid="{A57EE78B-8CA9-49B0-AA40-6DB76DB07CFF}">
+    <sortState ref="A2:D97">
+      <sortCondition sortBy="cellColor" ref="D1:D97" dxfId="1"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:D97">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>OR($D2=_xlfn.MINIFS($D$2:$D$97,$A$2:$A$97,$F$2:$F$8),$D2=_xlfn.MAXIFS($D$2:$D$97,$A$2:$A$97,$F$2:$F$8))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3" xr:uid="{F46421BF-A3D5-4A59-8EED-26D4952811E2}">
+      <formula1>$F$2:$F$8</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F9D316-38FB-48A5-9D50-4F255D0AAADD}">
   <dimension ref="B3:G13"/>
@@ -1359,27 +3270,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="5" operator="equal">
       <formula>"Kolkata"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E13">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="3" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F13">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="lessThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2123,16 +4034,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C14">
-    <cfRule type="top10" dxfId="3" priority="5" rank="5"/>
+    <cfRule type="top10" dxfId="43" priority="5" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D14">
-    <cfRule type="top10" dxfId="2" priority="4" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="42" priority="4" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E14">
-    <cfRule type="aboveAverage" dxfId="1" priority="2"/>
+    <cfRule type="aboveAverage" dxfId="41" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F14">
-    <cfRule type="aboveAverage" dxfId="0" priority="1" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="40" priority="1" aboveAverage="0"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2141,26 +4052,2811 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A716E025-9B0C-4EE8-8AB0-58CF02E014DC}">
+  <dimension ref="A1:G97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="4">
+        <v>43290</v>
+      </c>
+      <c r="D2" s="4">
+        <v>33869</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="4">
+        <v>43125</v>
+      </c>
+      <c r="D3" s="4">
+        <v>32686</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="4">
+        <v>40311</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45824</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="4">
+        <v>42777</v>
+      </c>
+      <c r="D5" s="4">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="4">
+        <v>42402</v>
+      </c>
+      <c r="D6" s="4">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="4">
+        <v>44168</v>
+      </c>
+      <c r="D7" s="4">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="4">
+        <v>43371</v>
+      </c>
+      <c r="D8" s="4">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="4">
+        <v>40673</v>
+      </c>
+      <c r="D9" s="4">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43403</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="4">
+        <v>40822</v>
+      </c>
+      <c r="D11" s="4">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="4">
+        <v>43678</v>
+      </c>
+      <c r="D12" s="4">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4">
+        <v>43623</v>
+      </c>
+      <c r="D13" s="4">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="4">
+        <v>43233</v>
+      </c>
+      <c r="D14" s="4">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="4">
+        <v>40717</v>
+      </c>
+      <c r="D15" s="4">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="4">
+        <v>40397</v>
+      </c>
+      <c r="D16" s="4">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="4">
+        <v>40635</v>
+      </c>
+      <c r="D17" s="4">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="4">
+        <v>42970</v>
+      </c>
+      <c r="D18" s="4">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="4">
+        <v>40838</v>
+      </c>
+      <c r="D19" s="4">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="4">
+        <v>42496</v>
+      </c>
+      <c r="D20" s="4">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="4">
+        <v>42072</v>
+      </c>
+      <c r="D21" s="4">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="4">
+        <v>42272</v>
+      </c>
+      <c r="D22" s="4">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="4">
+        <v>44139</v>
+      </c>
+      <c r="D23" s="4">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="4">
+        <v>43358</v>
+      </c>
+      <c r="D24" s="4">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="4">
+        <v>42911</v>
+      </c>
+      <c r="D25" s="4">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="4">
+        <v>44235</v>
+      </c>
+      <c r="D26" s="4">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="4">
+        <v>42462</v>
+      </c>
+      <c r="D27" s="4">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="4">
+        <v>43129</v>
+      </c>
+      <c r="D28" s="4">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="4">
+        <v>44033</v>
+      </c>
+      <c r="D29" s="4">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="4">
+        <v>43442</v>
+      </c>
+      <c r="D30" s="4">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="4">
+        <v>43447</v>
+      </c>
+      <c r="D31" s="4">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="4">
+        <v>43980</v>
+      </c>
+      <c r="D32" s="4">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="4">
+        <v>42593</v>
+      </c>
+      <c r="D33" s="4">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="4">
+        <v>43216</v>
+      </c>
+      <c r="D34" s="4">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="4">
+        <v>44199</v>
+      </c>
+      <c r="D35" s="4">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="4">
+        <v>40837</v>
+      </c>
+      <c r="D36" s="4">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="4">
+        <v>42914</v>
+      </c>
+      <c r="D37" s="4">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="4">
+        <v>40429</v>
+      </c>
+      <c r="D38" s="4">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D39" s="4">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="4">
+        <v>43160</v>
+      </c>
+      <c r="D40" s="4">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="4">
+        <v>40667</v>
+      </c>
+      <c r="D41" s="4">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="4">
+        <v>42813</v>
+      </c>
+      <c r="D42" s="4">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="4">
+        <v>43624</v>
+      </c>
+      <c r="D43" s="4">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D44" s="4">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="4">
+        <v>43912</v>
+      </c>
+      <c r="D45" s="4">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" s="4">
+        <v>43053</v>
+      </c>
+      <c r="D46" s="4">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="4">
+        <v>42615</v>
+      </c>
+      <c r="D47" s="4">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="4">
+        <v>40414</v>
+      </c>
+      <c r="D48" s="4">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D49" s="4">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="4">
+        <v>44142</v>
+      </c>
+      <c r="D50" s="4">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="4">
+        <v>42067</v>
+      </c>
+      <c r="D51" s="4">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="4">
+        <v>42378</v>
+      </c>
+      <c r="D52" s="4">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4">
+        <v>40556</v>
+      </c>
+      <c r="D53" s="4">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="4">
+        <v>42954</v>
+      </c>
+      <c r="D54" s="4">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="4">
+        <v>42129</v>
+      </c>
+      <c r="D55" s="4">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="4">
+        <v>42220</v>
+      </c>
+      <c r="D56" s="4">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="4">
+        <v>42477</v>
+      </c>
+      <c r="D57" s="4">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="4">
+        <v>44382</v>
+      </c>
+      <c r="D58" s="4">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="4">
+        <v>42936</v>
+      </c>
+      <c r="D59" s="4">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="4">
+        <v>40519</v>
+      </c>
+      <c r="D60" s="4">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="4">
+        <v>42841</v>
+      </c>
+      <c r="D61" s="4">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="4">
+        <v>42995</v>
+      </c>
+      <c r="D62" s="4">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="4">
+        <v>44243</v>
+      </c>
+      <c r="D63" s="4">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="4">
+        <v>42144</v>
+      </c>
+      <c r="D64" s="4">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="4">
+        <v>42296</v>
+      </c>
+      <c r="D65" s="4">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D66" s="4">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="4">
+        <v>43791</v>
+      </c>
+      <c r="D67" s="4">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="4">
+        <v>44131</v>
+      </c>
+      <c r="D68" s="4">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="4">
+        <v>42428</v>
+      </c>
+      <c r="D69" s="4">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="4">
+        <v>42690</v>
+      </c>
+      <c r="D70" s="4">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="4">
+        <v>42359</v>
+      </c>
+      <c r="D71" s="4">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="4">
+        <v>40840</v>
+      </c>
+      <c r="D72" s="4">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="4">
+        <v>40880</v>
+      </c>
+      <c r="D73" s="4">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="4">
+        <v>42049</v>
+      </c>
+      <c r="D74" s="4">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="4">
+        <v>43582</v>
+      </c>
+      <c r="D75" s="4">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="4">
+        <v>43034</v>
+      </c>
+      <c r="D76" s="4">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="4">
+        <v>43060</v>
+      </c>
+      <c r="D77" s="4">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="4">
+        <v>43846</v>
+      </c>
+      <c r="D78" s="4">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="4">
+        <v>44162</v>
+      </c>
+      <c r="D79" s="4">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="4">
+        <v>43788</v>
+      </c>
+      <c r="D80" s="4">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="4">
+        <v>42864</v>
+      </c>
+      <c r="D81" s="4">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C82" s="4">
+        <v>42856</v>
+      </c>
+      <c r="D82" s="4">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" s="4">
+        <v>44122</v>
+      </c>
+      <c r="D83" s="4">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="4">
+        <v>40901</v>
+      </c>
+      <c r="D84" s="4">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="4">
+        <v>42430</v>
+      </c>
+      <c r="D85" s="4">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="4">
+        <v>43017</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="4">
+        <v>43174</v>
+      </c>
+      <c r="D87" s="4">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="4">
+        <v>43951</v>
+      </c>
+      <c r="D88" s="4">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="4">
+        <v>40870</v>
+      </c>
+      <c r="D89" s="4">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C90" s="4">
+        <v>42726</v>
+      </c>
+      <c r="D90" s="4">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="4">
+        <v>44229</v>
+      </c>
+      <c r="D91" s="4">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" s="4">
+        <v>42088</v>
+      </c>
+      <c r="D92" s="4">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C93" s="4">
+        <v>43218</v>
+      </c>
+      <c r="D93" s="4">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C94" s="4">
+        <v>40804</v>
+      </c>
+      <c r="D94" s="4">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C95" s="4">
+        <v>43609</v>
+      </c>
+      <c r="D95" s="4">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="4">
+        <v>40469</v>
+      </c>
+      <c r="D96" s="4">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" s="4">
+        <v>44179</v>
+      </c>
+      <c r="D97" s="4">
+        <v>30335</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:D97">
+    <cfRule type="expression" dxfId="31" priority="1">
+      <formula>$A2=$G$4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394C3562-0856-4744-9A9A-931AB11F0DA8}">
+  <dimension ref="A4:G100"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
+    <col min="6" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="9">
+        <v>43290</v>
+      </c>
+      <c r="D5" s="9">
+        <v>33869</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="9">
+        <v>43125</v>
+      </c>
+      <c r="D6" s="9">
+        <v>32686</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9">
+        <v>40311</v>
+      </c>
+      <c r="D7" s="9">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="9">
+        <v>42777</v>
+      </c>
+      <c r="D8" s="9">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="9">
+        <v>42402</v>
+      </c>
+      <c r="D9" s="9">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="9">
+        <v>44168</v>
+      </c>
+      <c r="D10" s="9">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="9">
+        <v>43371</v>
+      </c>
+      <c r="D11" s="9">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="9">
+        <v>40673</v>
+      </c>
+      <c r="D12" s="9">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="9">
+        <v>43403</v>
+      </c>
+      <c r="D13" s="9">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="9">
+        <v>40822</v>
+      </c>
+      <c r="D14" s="9">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="9">
+        <v>43678</v>
+      </c>
+      <c r="D15" s="9">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="9">
+        <v>43623</v>
+      </c>
+      <c r="D16" s="9">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="9">
+        <v>43233</v>
+      </c>
+      <c r="D17" s="9">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="9">
+        <v>40717</v>
+      </c>
+      <c r="D18" s="9">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="9">
+        <v>40397</v>
+      </c>
+      <c r="D19" s="9">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="9">
+        <v>40635</v>
+      </c>
+      <c r="D20" s="9">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="9">
+        <v>42970</v>
+      </c>
+      <c r="D21" s="9">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="9">
+        <v>40838</v>
+      </c>
+      <c r="D22" s="9">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="9">
+        <v>42496</v>
+      </c>
+      <c r="D23" s="9">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="9">
+        <v>42072</v>
+      </c>
+      <c r="D24" s="9">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="9">
+        <v>42272</v>
+      </c>
+      <c r="D25" s="9">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="9">
+        <v>44139</v>
+      </c>
+      <c r="D26" s="9">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="9">
+        <v>43358</v>
+      </c>
+      <c r="D27" s="9">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="9">
+        <v>42911</v>
+      </c>
+      <c r="D28" s="9">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="9">
+        <v>44235</v>
+      </c>
+      <c r="D29" s="9">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="9">
+        <v>42462</v>
+      </c>
+      <c r="D30" s="9">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="9">
+        <v>43129</v>
+      </c>
+      <c r="D31" s="9">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="9">
+        <v>44033</v>
+      </c>
+      <c r="D32" s="9">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="9">
+        <v>43442</v>
+      </c>
+      <c r="D33" s="9">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="9">
+        <v>43447</v>
+      </c>
+      <c r="D34" s="9">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="9">
+        <v>43980</v>
+      </c>
+      <c r="D35" s="9">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="9">
+        <v>42593</v>
+      </c>
+      <c r="D36" s="9">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="9">
+        <v>43216</v>
+      </c>
+      <c r="D37" s="9">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="9">
+        <v>44199</v>
+      </c>
+      <c r="D38" s="9">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="9">
+        <v>40837</v>
+      </c>
+      <c r="D39" s="9">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="9">
+        <v>42914</v>
+      </c>
+      <c r="D40" s="9">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="9">
+        <v>40429</v>
+      </c>
+      <c r="D41" s="9">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="9">
+        <v>40898</v>
+      </c>
+      <c r="D42" s="9">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="9">
+        <v>43160</v>
+      </c>
+      <c r="D43" s="9">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="9">
+        <v>40667</v>
+      </c>
+      <c r="D44" s="9">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="9">
+        <v>42813</v>
+      </c>
+      <c r="D45" s="9">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="9">
+        <v>43624</v>
+      </c>
+      <c r="D46" s="9">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="9">
+        <v>44169</v>
+      </c>
+      <c r="D47" s="9">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="9">
+        <v>43912</v>
+      </c>
+      <c r="D48" s="9">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="9">
+        <v>43053</v>
+      </c>
+      <c r="D49" s="9">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="9">
+        <v>42615</v>
+      </c>
+      <c r="D50" s="9">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="9">
+        <v>40414</v>
+      </c>
+      <c r="D51" s="9">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="9">
+        <v>44169</v>
+      </c>
+      <c r="D52" s="9">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="9">
+        <v>44142</v>
+      </c>
+      <c r="D53" s="9">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="9">
+        <v>42067</v>
+      </c>
+      <c r="D54" s="9">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="9">
+        <v>42378</v>
+      </c>
+      <c r="D55" s="9">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="9">
+        <v>40556</v>
+      </c>
+      <c r="D56" s="9">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="9">
+        <v>42954</v>
+      </c>
+      <c r="D57" s="9">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="9">
+        <v>42129</v>
+      </c>
+      <c r="D58" s="9">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" s="9">
+        <v>42220</v>
+      </c>
+      <c r="D59" s="9">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="9">
+        <v>42477</v>
+      </c>
+      <c r="D60" s="9">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="9">
+        <v>44382</v>
+      </c>
+      <c r="D61" s="9">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="9">
+        <v>42936</v>
+      </c>
+      <c r="D62" s="9">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="9">
+        <v>40519</v>
+      </c>
+      <c r="D63" s="9">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="9">
+        <v>42841</v>
+      </c>
+      <c r="D64" s="9">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" s="9">
+        <v>42995</v>
+      </c>
+      <c r="D65" s="9">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="9">
+        <v>44243</v>
+      </c>
+      <c r="D66" s="9">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" s="9">
+        <v>42144</v>
+      </c>
+      <c r="D67" s="9">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" s="9">
+        <v>42296</v>
+      </c>
+      <c r="D68" s="9">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="9">
+        <v>40898</v>
+      </c>
+      <c r="D69" s="9">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="9">
+        <v>43791</v>
+      </c>
+      <c r="D70" s="9">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="9">
+        <v>44131</v>
+      </c>
+      <c r="D71" s="9">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="9">
+        <v>42428</v>
+      </c>
+      <c r="D72" s="9">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="9">
+        <v>42690</v>
+      </c>
+      <c r="D73" s="9">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C74" s="9">
+        <v>42359</v>
+      </c>
+      <c r="D74" s="9">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="9">
+        <v>40840</v>
+      </c>
+      <c r="D75" s="9">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C76" s="9">
+        <v>40880</v>
+      </c>
+      <c r="D76" s="9">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="9">
+        <v>42049</v>
+      </c>
+      <c r="D77" s="9">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" s="9">
+        <v>43582</v>
+      </c>
+      <c r="D78" s="9">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C79" s="9">
+        <v>43034</v>
+      </c>
+      <c r="D79" s="9">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" s="9">
+        <v>43060</v>
+      </c>
+      <c r="D80" s="9">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C81" s="9">
+        <v>43846</v>
+      </c>
+      <c r="D81" s="9">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" s="9">
+        <v>44162</v>
+      </c>
+      <c r="D82" s="9">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C83" s="9">
+        <v>43788</v>
+      </c>
+      <c r="D83" s="9">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="9">
+        <v>42864</v>
+      </c>
+      <c r="D84" s="9">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C85" s="9">
+        <v>42856</v>
+      </c>
+      <c r="D85" s="9">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" s="9">
+        <v>44122</v>
+      </c>
+      <c r="D86" s="9">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C87" s="9">
+        <v>40901</v>
+      </c>
+      <c r="D87" s="9">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C88" s="9">
+        <v>42430</v>
+      </c>
+      <c r="D88" s="9">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C89" s="9">
+        <v>43017</v>
+      </c>
+      <c r="D89" s="9">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C90" s="9">
+        <v>43174</v>
+      </c>
+      <c r="D90" s="9">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C91" s="9">
+        <v>43951</v>
+      </c>
+      <c r="D91" s="9">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="9">
+        <v>40870</v>
+      </c>
+      <c r="D92" s="9">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C93" s="9">
+        <v>42726</v>
+      </c>
+      <c r="D93" s="9">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C94" s="9">
+        <v>44229</v>
+      </c>
+      <c r="D94" s="9">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C95" s="9">
+        <v>42088</v>
+      </c>
+      <c r="D95" s="9">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C96" s="9">
+        <v>43218</v>
+      </c>
+      <c r="D96" s="9">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C97" s="9">
+        <v>40804</v>
+      </c>
+      <c r="D97" s="9">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C98" s="9">
+        <v>43609</v>
+      </c>
+      <c r="D98" s="9">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C99" s="9">
+        <v>40469</v>
+      </c>
+      <c r="D99" s="9">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C100" s="9">
+        <v>44179</v>
+      </c>
+      <c r="D100" s="9">
+        <v>30335</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="expression" dxfId="26" priority="2">
+      <formula>$A6=$F$6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:D100">
+    <cfRule type="expression" dxfId="25" priority="1">
+      <formula>OR($A5=$F$6,$A5=$G$6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B9DD6B-8E9E-4D8A-92EA-08C3D695D5AD}">
   <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="15" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2169,125 +6865,125 @@
         <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C2" s="4">
-        <v>43290</v>
+        <v>43358</v>
       </c>
       <c r="D2" s="4">
-        <v>33869</v>
+        <v>49942</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4">
-        <v>43125</v>
+        <v>44169</v>
       </c>
       <c r="D3" s="4">
-        <v>32686</v>
+        <v>10251</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4">
-        <v>40311</v>
+        <v>43290</v>
       </c>
       <c r="D4" s="4">
-        <v>45824</v>
+        <v>33869</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4">
-        <v>42777</v>
+        <v>43125</v>
       </c>
       <c r="D5" s="4">
-        <v>19187</v>
+        <v>32686</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4">
-        <v>42402</v>
+        <v>40311</v>
       </c>
       <c r="D6" s="4">
-        <v>38592</v>
+        <v>45824</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4">
-        <v>44168</v>
+        <v>42777</v>
       </c>
       <c r="D7" s="4">
-        <v>35035</v>
+        <v>19187</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4">
-        <v>43371</v>
+        <v>42402</v>
       </c>
       <c r="D8" s="4">
-        <v>15650</v>
+        <v>38592</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4">
-        <v>40673</v>
+        <v>44168</v>
       </c>
       <c r="D9" s="4">
-        <v>23117</v>
+        <v>35035</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C10" s="4">
-        <v>43403</v>
+        <v>43371</v>
       </c>
       <c r="D10" s="4">
-        <v>32039</v>
+        <v>15650</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
@@ -2295,6 +6991,1424 @@
         <v>81</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="4">
+        <v>40673</v>
+      </c>
+      <c r="D11" s="4">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4">
+        <v>43403</v>
+      </c>
+      <c r="D12" s="4">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="4">
+        <v>40822</v>
+      </c>
+      <c r="D13" s="4">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="4">
+        <v>43678</v>
+      </c>
+      <c r="D14" s="4">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="4">
+        <v>43623</v>
+      </c>
+      <c r="D15" s="4">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="4">
+        <v>43233</v>
+      </c>
+      <c r="D16" s="4">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="4">
+        <v>40717</v>
+      </c>
+      <c r="D17" s="4">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="4">
+        <v>40397</v>
+      </c>
+      <c r="D18" s="4">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="4">
+        <v>40635</v>
+      </c>
+      <c r="D19" s="4">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="4">
+        <v>42970</v>
+      </c>
+      <c r="D20" s="4">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="4">
+        <v>40838</v>
+      </c>
+      <c r="D21" s="4">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="4">
+        <v>42496</v>
+      </c>
+      <c r="D22" s="4">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="4">
+        <v>42072</v>
+      </c>
+      <c r="D23" s="4">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="4">
+        <v>42272</v>
+      </c>
+      <c r="D24" s="4">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="4">
+        <v>44139</v>
+      </c>
+      <c r="D25" s="4">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="4">
+        <v>42911</v>
+      </c>
+      <c r="D26" s="4">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="4">
+        <v>44235</v>
+      </c>
+      <c r="D27" s="4">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="4">
+        <v>42462</v>
+      </c>
+      <c r="D28" s="4">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="4">
+        <v>43129</v>
+      </c>
+      <c r="D29" s="4">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="4">
+        <v>44033</v>
+      </c>
+      <c r="D30" s="4">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="4">
+        <v>43442</v>
+      </c>
+      <c r="D31" s="4">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="4">
+        <v>43447</v>
+      </c>
+      <c r="D32" s="4">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="4">
+        <v>43980</v>
+      </c>
+      <c r="D33" s="4">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="4">
+        <v>42593</v>
+      </c>
+      <c r="D34" s="4">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="4">
+        <v>43216</v>
+      </c>
+      <c r="D35" s="4">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="4">
+        <v>44199</v>
+      </c>
+      <c r="D36" s="4">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="4">
+        <v>40837</v>
+      </c>
+      <c r="D37" s="4">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="4">
+        <v>42914</v>
+      </c>
+      <c r="D38" s="4">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="4">
+        <v>40429</v>
+      </c>
+      <c r="D39" s="4">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C40" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D40" s="4">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" s="4">
+        <v>43160</v>
+      </c>
+      <c r="D41" s="4">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="4">
+        <v>40667</v>
+      </c>
+      <c r="D42" s="4">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="4">
+        <v>42813</v>
+      </c>
+      <c r="D43" s="4">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="4">
+        <v>43624</v>
+      </c>
+      <c r="D44" s="4">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="4">
+        <v>44169</v>
+      </c>
+      <c r="D45" s="4">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="4">
+        <v>43912</v>
+      </c>
+      <c r="D46" s="4">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" s="4">
+        <v>43053</v>
+      </c>
+      <c r="D47" s="4">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" s="4">
+        <v>42615</v>
+      </c>
+      <c r="D48" s="4">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="4">
+        <v>40414</v>
+      </c>
+      <c r="D49" s="4">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="4">
+        <v>44142</v>
+      </c>
+      <c r="D50" s="4">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="4">
+        <v>42067</v>
+      </c>
+      <c r="D51" s="4">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="4">
+        <v>42378</v>
+      </c>
+      <c r="D52" s="4">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4">
+        <v>40556</v>
+      </c>
+      <c r="D53" s="4">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="4">
+        <v>42954</v>
+      </c>
+      <c r="D54" s="4">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="4">
+        <v>42129</v>
+      </c>
+      <c r="D55" s="4">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="4">
+        <v>42220</v>
+      </c>
+      <c r="D56" s="4">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="4">
+        <v>42477</v>
+      </c>
+      <c r="D57" s="4">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="4">
+        <v>44382</v>
+      </c>
+      <c r="D58" s="4">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="4">
+        <v>42936</v>
+      </c>
+      <c r="D59" s="4">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="4">
+        <v>40519</v>
+      </c>
+      <c r="D60" s="4">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="4">
+        <v>42841</v>
+      </c>
+      <c r="D61" s="4">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C62" s="4">
+        <v>42995</v>
+      </c>
+      <c r="D62" s="4">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="4">
+        <v>44243</v>
+      </c>
+      <c r="D63" s="4">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="4">
+        <v>42144</v>
+      </c>
+      <c r="D64" s="4">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="4">
+        <v>42296</v>
+      </c>
+      <c r="D65" s="4">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="4">
+        <v>40898</v>
+      </c>
+      <c r="D66" s="4">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="4">
+        <v>43791</v>
+      </c>
+      <c r="D67" s="4">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="4">
+        <v>44131</v>
+      </c>
+      <c r="D68" s="4">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="4">
+        <v>42428</v>
+      </c>
+      <c r="D69" s="4">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="4">
+        <v>42690</v>
+      </c>
+      <c r="D70" s="4">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="4">
+        <v>42359</v>
+      </c>
+      <c r="D71" s="4">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="4">
+        <v>40840</v>
+      </c>
+      <c r="D72" s="4">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="4">
+        <v>40880</v>
+      </c>
+      <c r="D73" s="4">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="4">
+        <v>42049</v>
+      </c>
+      <c r="D74" s="4">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="4">
+        <v>43582</v>
+      </c>
+      <c r="D75" s="4">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="4">
+        <v>43034</v>
+      </c>
+      <c r="D76" s="4">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" s="4">
+        <v>43060</v>
+      </c>
+      <c r="D77" s="4">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="4">
+        <v>43846</v>
+      </c>
+      <c r="D78" s="4">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="4">
+        <v>44162</v>
+      </c>
+      <c r="D79" s="4">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="4">
+        <v>43788</v>
+      </c>
+      <c r="D80" s="4">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C81" s="4">
+        <v>42864</v>
+      </c>
+      <c r="D81" s="4">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C82" s="4">
+        <v>42856</v>
+      </c>
+      <c r="D82" s="4">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" s="4">
+        <v>44122</v>
+      </c>
+      <c r="D83" s="4">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="4">
+        <v>40901</v>
+      </c>
+      <c r="D84" s="4">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="4">
+        <v>42430</v>
+      </c>
+      <c r="D85" s="4">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="4">
+        <v>43017</v>
+      </c>
+      <c r="D86" s="4">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="4">
+        <v>43174</v>
+      </c>
+      <c r="D87" s="4">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="4">
+        <v>43951</v>
+      </c>
+      <c r="D88" s="4">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="4">
+        <v>40870</v>
+      </c>
+      <c r="D89" s="4">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C90" s="4">
+        <v>42726</v>
+      </c>
+      <c r="D90" s="4">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="4">
+        <v>44229</v>
+      </c>
+      <c r="D91" s="4">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" s="4">
+        <v>42088</v>
+      </c>
+      <c r="D92" s="4">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C93" s="4">
+        <v>43218</v>
+      </c>
+      <c r="D93" s="4">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C94" s="4">
+        <v>40804</v>
+      </c>
+      <c r="D94" s="4">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C95" s="4">
+        <v>43609</v>
+      </c>
+      <c r="D95" s="4">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="4">
+        <v>40469</v>
+      </c>
+      <c r="D96" s="4">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" s="4">
+        <v>44179</v>
+      </c>
+      <c r="D97" s="4">
+        <v>30335</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D97" xr:uid="{BE7746A6-18F7-4660-A0D5-9347EEEC0064}">
+    <sortState ref="A2:D97">
+      <sortCondition sortBy="cellColor" ref="A1:A97" dxfId="18"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:D97">
+    <cfRule type="expression" dxfId="20" priority="1">
+      <formula>OR($D2=MIN($D$2:$D$97),$D2=MAX($D$2:$D$97))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA98D26A-22D5-41C8-BF05-53DC65AE44A2}">
+  <dimension ref="A1:G97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="4">
+        <v>43290</v>
+      </c>
+      <c r="D2" s="4">
+        <v>33869</v>
+      </c>
+      <c r="E2" t="e">
+        <f ca="1">unique(A2:A97)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="4">
+        <v>43125</v>
+      </c>
+      <c r="D3" s="4">
+        <v>32686</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="4">
+        <v>40311</v>
+      </c>
+      <c r="D4" s="4">
+        <v>45824</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="4">
+        <v>42777</v>
+      </c>
+      <c r="D5" s="4">
+        <v>19187</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="4">
+        <v>42402</v>
+      </c>
+      <c r="D6" s="4">
+        <v>38592</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="4">
+        <v>44168</v>
+      </c>
+      <c r="D7" s="4">
+        <v>35035</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="4">
+        <v>43371</v>
+      </c>
+      <c r="D8" s="4">
+        <v>15650</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="4">
+        <v>40673</v>
+      </c>
+      <c r="D9" s="4">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4">
+        <v>43403</v>
+      </c>
+      <c r="D10" s="4">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C11" s="4">
@@ -2304,7 +8418,7 @@
         <v>38562</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
@@ -2318,7 +8432,7 @@
         <v>43948</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
@@ -2332,7 +8446,7 @@
         <v>27580</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>81</v>
       </c>
@@ -2346,7 +8460,7 @@
         <v>19377</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>81</v>
       </c>
@@ -2360,7 +8474,7 @@
         <v>26799</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>73</v>
       </c>
@@ -3509,6 +9623,18 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D97" xr:uid="{A57EE78B-8CA9-49B0-AA40-6DB76DB07CFF}"/>
+  <conditionalFormatting sqref="A2:D97">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>AND($A2=$G$3,OR($D2=_xlfn.MINIFS($D$2:$D$97,$A$2:$A$97,$G$3),$D2=_xlfn.MAXIFS($D$2:$D$97,$A$2:$A$97,$G$3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3" xr:uid="{3564CA62-8FC1-4528-9CCB-312DA9D4133D}">
+      <formula1>$F$2:$F$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>